--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -39,7 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006C4FD8"/>
+        <fgColor rgb="000D9488"/>
       </patternFill>
     </fill>
   </fills>
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -483,207 +483,207 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAC001</t>
+          <t>OFA001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leche Evaporada Entera 400g</t>
+          <t>Asado de Tira Importado USA kg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lácteos</t>
+          <t>CARNE DE RES IMPORTADA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.5</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>🥛</t>
+          <t>🥩</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>data/img/LAC001.jpg</t>
+          <t>data/img/OFA001.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LAC002</t>
+          <t>ADS010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leche Condensada 397g</t>
+          <t>Lomo Fino de Res Nacional kg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lácteos</t>
+          <t>CARNE DE RES NACIONAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.8</v>
+        <v>47.5</v>
       </c>
       <c r="F3" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🥫</t>
+          <t>🥩</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/img/LAC002.jpg</t>
+          <t>data/img/ADS010.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LAC003</t>
+          <t>ALB005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yogurt Fresa 1L</t>
+          <t>Pollo Entero Trozado kg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lácteos</t>
+          <t>AVES NACIONAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6.2</v>
+        <v>12.4</v>
       </c>
       <c r="F4" t="n">
-        <v>95</v>
+        <v>520</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🥤</t>
+          <t>🍗</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/img/LAC003.jpg</t>
+          <t>data/img/ALB005.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LAC004</t>
+          <t>AIB002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Queso Fresco 500g</t>
+          <t>Pechuga de Pavo Importada kg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lácteos</t>
+          <t>AVES IMPORTADAS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12.9</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🧀</t>
+          <t>🦃</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/img/LAC004.jpg</t>
+          <t>data/img/AIB002.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAC005</t>
+          <t>LAH017</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mantequilla con Sal 200g</t>
+          <t>Bondiola de Cerdo kg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lácteos</t>
+          <t>CARNICOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7.4</v>
+        <v>21.5</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🧈</t>
+          <t>🥓</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/img/LAC005.jpg</t>
+          <t>data/img/LAH017.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABA001</t>
+          <t>LAA007</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fideos Spaghetti 500g</t>
+          <t>Queso Edam Bonlé 1kg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abarrotes</t>
+          <t>QUESOS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,74 +692,74 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.9</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🍝</t>
+          <t>🧀</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/img/ABA001.jpg</t>
+          <t>data/img/LAA007.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABA002</t>
+          <t>LAA021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arroz Extra 5kg</t>
+          <t>Queso Parmesano Rallado 500g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Abarrotes</t>
+          <t>QUESOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BOLSA</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>23.5</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="n">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🍚</t>
+          <t>🧀</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/img/ABA002.jpg</t>
+          <t>data/img/LAA021.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABA003</t>
+          <t>LAB004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Azúcar Rubia 1kg</t>
+          <t>Leche Fresca Entera 1L</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abarrotes</t>
+          <t>LECHES FRESCAS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -768,36 +768,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="F9" t="n">
-        <v>260</v>
+        <v>430</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🧂</t>
+          <t>🥛</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/img/ABA003.jpg</t>
+          <t>data/img/LAB004.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABA004</t>
+          <t>LAD002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aceite Vegetal 1L</t>
+          <t>Leche Evaporada Gloria 400g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Abarrotes</t>
+          <t>EVAPORADAS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -806,36 +806,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="F10" t="n">
-        <v>180</v>
+        <v>980</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🫗</t>
+          <t>🥫</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/img/ABA004.jpg</t>
+          <t>data/img/LAD002.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ABA005</t>
+          <t>LCC001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atún en Aceite 170g</t>
+          <t>Leche Condensada Nestlé 1kg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abarrotes</t>
+          <t>LECHE CONDENSADA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -844,36 +844,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="F11" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🐟</t>
+          <t>🥫</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/img/ABA005.jpg</t>
+          <t>data/img/LCC001.jpg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABA006</t>
+          <t>LAG012</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Harina sin Preparar 1kg</t>
+          <t>Yogurt Bebible Fresa 1L</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Abarrotes</t>
+          <t>YOGURTS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="F12" t="n">
-        <v>150</v>
+        <v>360</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🌾</t>
+          <t>🥤</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/img/ABA006.jpg</t>
+          <t>data/img/LAG012.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOL001</t>
+          <t>LAG055</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chocolate Barra 90g</t>
+          <t>Yogurt Griego Natural 1kg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Golosinas</t>
+          <t>YOGURTS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -920,150 +920,150 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.2</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🍫</t>
+          <t>🍶</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/img/GOL001.jpg</t>
+          <t>data/img/LAG055.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOL002</t>
+          <t>LAE004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Galletas Vainilla x6</t>
+          <t>Mantequilla Sin Sal Premium 1kg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Golosinas</t>
+          <t>MANTEQUILLAS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PACK</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🍪</t>
+          <t>🧈</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/img/GOL002.jpg</t>
+          <t>data/img/LAE004.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOL003</t>
+          <t>LAF008</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caramelos Surtidos Bolsa 1kg</t>
+          <t>Manjar Blanco Repostero 1kg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Golosinas</t>
+          <t>MANJARES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BOLSA</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🍬</t>
+          <t>🍮</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/img/GOL003.jpg</t>
+          <t>data/img/LAF008.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BEB001</t>
+          <t>IGA003</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gaseosa Cola 3L</t>
+          <t>Aceite Vegetal Premium 5L</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>ACEITES Y GRASAS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>BIDON</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.5</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>🥤</t>
+          <t>🫗</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/img/BEB001.jpg</t>
+          <t>data/img/IGA003.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BEB002</t>
+          <t>OSB005</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agua Mineral 625ml</t>
+          <t>Aceite de Oliva Extra Virgen 1L</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>ACEITES Y GRASAS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1072,36 +1072,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>520</v>
+        <v>75</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>💧</t>
+          <t>🫒</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/img/BEB002.jpg</t>
+          <t>data/img/OSB005.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BEB003</t>
+          <t>AEA006</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jugo de Durazno 1L</t>
+          <t>Caldo de Gallina Deshidratado 1kg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>SOPAS SUSTANCIAS Y CREMAS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1110,36 +1110,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.3</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🧃</t>
+          <t>🍲</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/img/BEB003.jpg</t>
+          <t>data/img/AEA006.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LIM001</t>
+          <t>LAP002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Detergente en Polvo 900g</t>
+          <t>Demiglace de Vino Tinto 1kg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Limpieza</t>
+          <t>SOPAS SUSTANCIAS Y CREMAS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1148,95 +1148,703 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>🧼</t>
+          <t>🍲</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/img/LIM001.jpg</t>
+          <t>data/img/LAP002.jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LIM002</t>
+          <t>GLO008</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jabón de Tocador 90g</t>
+          <t>Filete de Atún en Aceite 1kg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Limpieza</t>
+          <t>CONSERVAS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>LATA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.1</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>🧴</t>
+          <t>🐟</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/img/LIM002.jpg</t>
+          <t>data/img/GLO008.jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LIM003</t>
+          <t>OSE003</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lejía 1L</t>
+          <t>Durazno en Mitades 820g</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Limpieza</t>
+          <t>CONSERVAS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>LATA</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>310</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>🍑</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>data/img/OSE003.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OSF010</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pasta de Tomate 3kg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SALSAS Y PASTAS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LATA</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" t="n">
+        <v>170</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>data/img/OSF010.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OSF021</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Salsa de Ostión 500ml</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SALSAS Y PASTAS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F21" t="n">
-        <v>175</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>🪣</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>data/img/LIM003.jpg</t>
+      <c r="E23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" t="n">
+        <v>90</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>🍶</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>data/img/OSF021.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AJA007</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Glutamato Monosódico 1kg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CONDIMENTOS PROCESADOS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>140</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>data/img/AJA007.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CKA011</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pimienta Negra Molida 500g</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CONDIMENTOS SIN PROCESAR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>28</v>
+      </c>
+      <c r="F25" t="n">
+        <v>65</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>data/img/CKA011.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CCA004</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Agua Mineral Sin Gas 625ml x15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AGUA MINERAL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PACK</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="n">
+        <v>400</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>data/img/CCA004.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LAK002</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gaseosa Cola 3L</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BEBIDAS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>280</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>🥤</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>data/img/LAK002.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CNA006</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cobertura Bitter 70% 2.5kg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>COBERTURAS CHOCOLATES Y OTROS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>64</v>
+      </c>
+      <c r="F28" t="n">
+        <v>55</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>🍫</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>data/img/CNA006.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CNV003</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gelatina Sin Sabor 500g</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CONFITERIA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" t="n">
+        <v>95</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>🍮</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>data/img/CNV003.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FDA002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fideo Spaghetti Don Vittorio 5kg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FIDEOS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>26</v>
+      </c>
+      <c r="F30" t="n">
+        <v>230</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>🍝</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>data/img/FDA002.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ARA001</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Arroz Superior Añejo 50kg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ARROZ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SACO</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>165</v>
+      </c>
+      <c r="F31" t="n">
+        <v>120</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>🍚</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>data/img/ARA001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AZA001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Azúcar Rubia Doméstica 50kg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AZUCAR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SACO</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>145</v>
+      </c>
+      <c r="F32" t="n">
+        <v>110</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>data/img/AZA001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HVA001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Huevos Pardos Frescos x30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HUEVOS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PACK</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>16</v>
+      </c>
+      <c r="F33" t="n">
+        <v>340</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>🥚</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>data/img/HVA001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MRA003</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Langostino Entero Congelado kg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MARISCOS Y CONGELADOS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>38</v>
+      </c>
+      <c r="F34" t="n">
+        <v>80</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>🦐</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>data/img/MRA003.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PCA001</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Papa Bastón Congelada 2.5kg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PAPAS CONGELADAS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>260</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>🍟</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>data/img/PCA001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VGA004</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mix de Vegetales Congelado 1kg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VERDURAS CONGELADAS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>190</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>🥦</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>data/img/VGA004.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LBA005</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pulpa de Maracuyá Congelada 1kg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FRUTAS CONGELADAS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" t="n">
+        <v>130</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>🥭</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>data/img/LBA005.jpg</t>
         </is>
       </c>
     </row>
